--- a/Conf Materials/abstract_results.xlsx
+++ b/Conf Materials/abstract_results.xlsx
@@ -2,20 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unioxfordnexus-my.sharepoint.com/personal/orms1149_ox_ac_uk/Documents/Documents/GitHub/OMOP-Validation-Study/Conf Materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="96" documentId="8_{9A747781-F094-4C57-98FC-633BE8F4A078}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D04AA215-CF74-46C9-AE38-3316B4358C33}"/>
+  <xr:revisionPtr revIDLastSave="131" documentId="8_{9A747781-F094-4C57-98FC-633BE8F4A078}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A63A2D1A-8CCB-4A32-8ED6-AEFB033F9B3C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9E5C5CCE-F48E-47C7-82F8-E2004C3D7CB4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -56,12 +56,30 @@
     <t>Unadjusted mean visits (CI)  - overall</t>
   </si>
   <si>
+    <t>22.9 (22.556, 23.26)</t>
+  </si>
+  <si>
+    <t>21.4 (21.037, 21.762)</t>
+  </si>
+  <si>
     <t>Unadjusted mean visits (CI) - year 1</t>
   </si>
   <si>
+    <t>13.7 (13.480, 13.892)</t>
+  </si>
+  <si>
+    <t>13.93 (13.713, 14.146)</t>
+  </si>
+  <si>
     <t>Unadjusted mean visits (CI) - year 2</t>
   </si>
   <si>
+    <t>9.22 (9.042, 9.394)</t>
+  </si>
+  <si>
+    <t>7.47 (7.289, 7.647)</t>
+  </si>
+  <si>
     <t>Number of patients identified in both datasets (same ids)</t>
   </si>
   <si>
@@ -74,95 +92,77 @@
     <t>GP </t>
   </si>
   <si>
+    <t>343,369 (82.7%)</t>
+  </si>
+  <si>
+    <t>277,738 (73.3%)</t>
+  </si>
+  <si>
     <t>Nurse</t>
   </si>
   <si>
+    <t>35,745 (8.61%)</t>
+  </si>
+  <si>
+    <t>28,892 (7.63%)</t>
+  </si>
+  <si>
     <t>Other</t>
   </si>
   <si>
+    <t>36,156 (8.71%)</t>
+  </si>
+  <si>
+    <t>50,649 (13.4%)</t>
+  </si>
+  <si>
     <t>Uncategorised</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
+    <t>21,569 (5.69%)</t>
+  </si>
+  <si>
     <t>Unadjusted mean costs (CI) - overall</t>
   </si>
   <si>
+    <t>894.16 (880.897, 907.86)</t>
+  </si>
+  <si>
+    <t>829.76 (816.167, 843.524)</t>
+  </si>
+  <si>
     <t>Unadjusted mean costs (CI) - year 1</t>
   </si>
   <si>
+    <t>532.65 (524.983, 540.655)</t>
+  </si>
+  <si>
+    <t>537.88 (529.572, 546.637)</t>
+  </si>
+  <si>
     <t>Unadjusted mean costs (CI) - year 2</t>
   </si>
   <si>
+    <t>361.51 (354.582, 368.220)</t>
+  </si>
+  <si>
+    <t>291.88 (285.105, 298.903)</t>
+  </si>
+  <si>
     <t>Plot for primary care visits unadjusted (all patients)</t>
   </si>
   <si>
     <t>Plot for primary care costs unadjusted (all patients</t>
-  </si>
-  <si>
-    <t>21.4 (21.037, 21.762)</t>
-  </si>
-  <si>
-    <t>13.93 (13.713, 14.146)</t>
-  </si>
-  <si>
-    <t>7.47 (7.289, 7.647)</t>
-  </si>
-  <si>
-    <t>22.9 (22.556, 23.26)</t>
-  </si>
-  <si>
-    <t>894.16 (880.897, 907.86)</t>
-  </si>
-  <si>
-    <t>13.7 (13.480, 13.892)</t>
-  </si>
-  <si>
-    <t>9.22 (9.042, 9.394)</t>
-  </si>
-  <si>
-    <t>532.65 (524.983, 540.655)</t>
-  </si>
-  <si>
-    <t>361.51 (354.582, 368.220)</t>
-  </si>
-  <si>
-    <t>343,369 (82.7%)</t>
-  </si>
-  <si>
-    <t>35,745 (8.61%)</t>
-  </si>
-  <si>
-    <t>36,156 (8.71%)</t>
-  </si>
-  <si>
-    <t>277,738 (73.3%)</t>
-  </si>
-  <si>
-    <t>28,892 (7.63%)</t>
-  </si>
-  <si>
-    <t>50,649 (13.4%)</t>
-  </si>
-  <si>
-    <t>21,569 (5.69%)</t>
-  </si>
-  <si>
-    <t>891.29 (875.522, 905.886)</t>
-  </si>
-  <si>
-    <t>572.73 (563.465, 582.595)</t>
-  </si>
-  <si>
-    <t>311.01 (303.497, 318.747)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -190,13 +190,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFC00000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -218,7 +211,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -229,28 +222,22 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -273,23 +260,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>3550920</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>152412</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>9</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>365772</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>7629</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 6">
+        <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1449EEC3-E738-D26D-417C-1BE85B15800A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{004C41BA-9657-1519-7B83-9AE98F4C9311}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -311,7 +298,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3627120" y="3474720"/>
+          <a:off x="3550920" y="3665220"/>
           <a:ext cx="5943612" cy="4572009"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -323,23 +310,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>9</xdr:col>
+      <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
+      <xdr:col>17</xdr:col>
       <xdr:colOff>457212</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>43</xdr:row>
       <xdr:rowOff>9</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 8">
+        <xdr:cNvPr id="5" name="Picture 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8C075FE-C85B-8D49-F991-48E1333BE10C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{99967462-70F7-9F22-C33F-1A4CBFAFD540}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -361,7 +348,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10027920" y="3474720"/>
+          <a:off x="9738360" y="3291840"/>
           <a:ext cx="5943612" cy="4572009"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -699,18 +686,17 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="52.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="22.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="12"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C1" s="9"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
@@ -719,7 +705,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -730,7 +716,7 @@
         <v>17705</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -741,144 +727,143 @@
         <v>534.79999999999995</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="9">
+        <v>14</v>
+      </c>
+      <c r="B8" s="10">
         <v>17426</v>
       </c>
-      <c r="C8" s="8"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C8" s="10"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="10">
+        <v>15</v>
+      </c>
+      <c r="B9" s="6">
         <v>17639</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="6">
         <v>16978</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="11" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C15" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="11" t="s">
+      <c r="C16" s="4" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="D16" s="4"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C17" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="D17" s="7"/>
+        <v>35</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D17" s="5"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
@@ -887,14 +872,14 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
